--- a/dal_quiz_logic.xlsx
+++ b/dal_quiz_logic.xlsx
@@ -2965,7 +2965,7 @@
       </c>
       <c r="B3" s="470" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -7928,52 +7928,52 @@
       <c r="D15" s="409" t="n"/>
       <c r="E15" s="323" t="inlineStr">
         <is>
-          <t>You pursue questions until you find the answer — then you find a better question.</t>
+          <t>Driven by questions, comfortable with complexity, at home in a lab or library.</t>
         </is>
       </c>
       <c r="F15" s="324" t="inlineStr">
         <is>
-          <t>You're not satisfied until an idea becomes something real that works.</t>
+          <t>Turns ideas into physical things — happiest when building something that actually works.</t>
         </is>
       </c>
       <c r="G15" s="325" t="inlineStr">
         <is>
-          <t>You see the logic underneath everything and build systems that think.</t>
+          <t>Sees systems and patterns where others see noise — code and data are a native language.</t>
         </is>
       </c>
       <c r="H15" s="326" t="inlineStr">
         <is>
-          <t>You imagine what a space could be before anyone else sees it.</t>
+          <t>Thinks spatially — imagines what a space, building, or neighbourhood could become.</t>
         </is>
       </c>
       <c r="I15" s="327" t="inlineStr">
         <is>
-          <t>You believe the future depends on how we treat living systems.</t>
+          <t>Hands-on steward of living systems — farms, forests, fisheries, and the animals within them.</t>
         </is>
       </c>
       <c r="J15" s="328" t="inlineStr">
         <is>
-          <t>You feel most alive outdoors, at sea, or in the field where real systems live.</t>
+          <t>Field scientist at heart — most alive when investigating how natural systems actually work.</t>
         </is>
       </c>
       <c r="K15" s="329" t="inlineStr">
         <is>
-          <t>You notice when people are struggling and feel called to help them thrive.</t>
+          <t>Attuned to how people are doing and motivated to help them function and flourish.</t>
         </is>
       </c>
       <c r="L15" s="330" t="inlineStr">
         <is>
-          <t>You set a goal, build a plan, and make it happen.</t>
+          <t>Goal-oriented and commercially minded — builds plans, builds teams, builds things that scale.</t>
         </is>
       </c>
       <c r="M15" s="331" t="inlineStr">
         <is>
-          <t>You want to understand what makes societies work — and fix what doesn't.</t>
+          <t>Asks how societies work and why they don't — drawn to law, policy, advocacy, and change.</t>
         </is>
       </c>
       <c r="N15" s="332" t="inlineStr">
         <is>
-          <t>You process the world through expression and make others feel what you feel.</t>
+          <t>Processes the world through making — writing, music, visual art, or performance.</t>
         </is>
       </c>
     </row>
